--- a/data/trans_orig/MCS12_SP_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140429</t>
+          <t>138800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180921</t>
+          <t>179080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178646</t>
+          <t>179663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220414</t>
+          <t>220539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>331308</t>
+          <t>330703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>390130</t>
+          <t>390176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>313143</t>
+          <t>314984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>353635</t>
+          <t>355264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247075</t>
+          <t>246950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288843</t>
+          <t>287826</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>571423</t>
+          <t>571377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>630245</t>
+          <t>630850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>226060</t>
+          <t>230931</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>278843</t>
+          <t>280456</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>279582</t>
+          <t>278497</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>331441</t>
+          <t>329391</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>519621</t>
+          <t>524290</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>594422</t>
+          <t>595734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456646</t>
+          <t>455033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>509429</t>
+          <t>504558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>294053</t>
+          <t>296103</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345912</t>
+          <t>346997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>766560</t>
+          <t>765248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>841361</t>
+          <t>836692</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>254122</t>
+          <t>252290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>302328</t>
+          <t>306203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>374629</t>
+          <t>373700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>427406</t>
+          <t>428926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>640673</t>
+          <t>647623</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>716116</t>
+          <t>715925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>336340</t>
+          <t>332465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>384546</t>
+          <t>386378</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>262338</t>
+          <t>260818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>315115</t>
+          <t>316044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>612296</t>
+          <t>612487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>687739</t>
+          <t>680789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>210914</t>
+          <t>211625</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256654</t>
+          <t>257941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>298972</t>
+          <t>300237</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>343456</t>
+          <t>344864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>522955</t>
+          <t>522273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>588922</t>
+          <t>587914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262493</t>
+          <t>261206</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308233</t>
+          <t>307522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172186</t>
+          <t>170778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216670</t>
+          <t>215405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>445867</t>
+          <t>446875</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>511834</t>
+          <t>512516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>197741</t>
+          <t>197201</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>236626</t>
+          <t>238022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>218454</t>
+          <t>218838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>257927</t>
+          <t>258174</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>424081</t>
+          <t>427016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>480553</t>
+          <t>484017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150084</t>
+          <t>148688</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188969</t>
+          <t>189509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>146059</t>
+          <t>145812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185532</t>
+          <t>185148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310143</t>
+          <t>306679</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>366615</t>
+          <t>363680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>45,99%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139721</t>
+          <t>141528</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175148</t>
+          <t>175895</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>178894</t>
+          <t>177176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212688</t>
+          <t>211622</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>331142</t>
+          <t>331835</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>378096</t>
+          <t>380219</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,83%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>117435</t>
+          <t>116688</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>152862</t>
+          <t>151055</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130246</t>
+          <t>131312</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164040</t>
+          <t>165758</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>257421</t>
+          <t>255298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>304375</t>
+          <t>303682</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101754</t>
+          <t>99940</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128512</t>
+          <t>129291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>149550</t>
+          <t>150156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187769</t>
+          <t>186824</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259941</t>
+          <t>261032</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>306537</t>
+          <t>305440</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,17%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81371</t>
+          <t>80592</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108129</t>
+          <t>109943</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>146139</t>
+          <t>147084</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>184358</t>
+          <t>183752</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>237254</t>
+          <t>238351</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283850</t>
+          <t>282759</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1356877</t>
+          <t>1359326</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1473889</t>
+          <t>1474346</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1773088</t>
+          <t>1770768</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1890301</t>
+          <t>1893868</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3167492</t>
+          <t>3159395</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3328852</t>
+          <t>3321312</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1802654</t>
+          <t>1802197</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1919666</t>
+          <t>1917217</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1488896</t>
+          <t>1485329</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1606109</t>
+          <t>1608429</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3326889</t>
+          <t>3334429</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3488249</t>
+          <t>3496346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,53%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140438</t>
+          <t>139018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180513</t>
+          <t>181152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191075</t>
+          <t>192100</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>232027</t>
+          <t>233165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>342731</t>
+          <t>342855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>401964</t>
+          <t>400277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273633</t>
+          <t>272994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>313708</t>
+          <t>315128</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198203</t>
+          <t>197065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239155</t>
+          <t>238130</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>482412</t>
+          <t>484099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>541645</t>
+          <t>541521</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>278908</t>
+          <t>279757</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>332454</t>
+          <t>334066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>314021</t>
+          <t>312935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>364228</t>
+          <t>364796</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>607766</t>
+          <t>606594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>682615</t>
+          <t>680481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,45%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354633</t>
+          <t>353021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408179</t>
+          <t>407330</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246027</t>
+          <t>245459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296234</t>
+          <t>297320</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>614727</t>
+          <t>616861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>689576</t>
+          <t>690748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>320139</t>
+          <t>319946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>372448</t>
+          <t>374084</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>424844</t>
+          <t>424174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>478815</t>
+          <t>481088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>758290</t>
+          <t>760064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>837582</t>
+          <t>836641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309415</t>
+          <t>307779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>361724</t>
+          <t>361917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232035</t>
+          <t>229762</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286006</t>
+          <t>286676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>555130</t>
+          <t>556071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>632648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>303279</t>
+          <t>303973</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>357153</t>
+          <t>356194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>368154</t>
+          <t>370624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>419090</t>
+          <t>420476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>689841</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>762897</t>
+          <t>762624</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>257464</t>
+          <t>258423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311338</t>
+          <t>310644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>197109</t>
+          <t>195723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248045</t>
+          <t>245575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>467919</t>
+          <t>468192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>540975</t>
+          <t>536961</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>215348</t>
+          <t>213603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>258342</t>
+          <t>257552</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285006</t>
+          <t>287071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>327626</t>
+          <t>326885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>515417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>571204</t>
+          <t>575818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,64%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171087</t>
+          <t>171877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>214081</t>
+          <t>215826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120174</t>
+          <t>120915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162794</t>
+          <t>160729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306025</t>
+          <t>301411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>364223</t>
+          <t>361812</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>137063</t>
+          <t>138375</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>174701</t>
+          <t>175511</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>211708</t>
+          <t>211167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>246566</t>
+          <t>247537</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>360931</t>
+          <t>357055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>414002</t>
+          <t>409963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>61,76%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>135085</t>
+          <t>134275</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>172723</t>
+          <t>171411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>107430</t>
+          <t>106459</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142288</t>
+          <t>142829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249780</t>
+          <t>253819</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>302851</t>
+          <t>306727</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126614</t>
+          <t>126117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160651</t>
+          <t>159348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>246079</t>
+          <t>245740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283176</t>
+          <t>284163</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>382548</t>
+          <t>380763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>432945</t>
+          <t>434373</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89200</t>
+          <t>90503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123237</t>
+          <t>123734</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105803</t>
+          <t>104816</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>142900</t>
+          <t>143239</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>205885</t>
+          <t>204457</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>256282</t>
+          <t>258067</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1620190</t>
+          <t>1621155</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1738378</t>
+          <t>1735304</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2141823</t>
+          <t>2141157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2259257</t>
+          <t>2255406</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3790831</t>
+          <t>3799360</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3959656</t>
+          <t>3968661</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1688401</t>
+          <t>1691475</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1806589</t>
+          <t>1805624</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1299052</t>
+          <t>1302903</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1416486</t>
+          <t>1417152</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3025432</t>
+          <t>3016427</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3194257</t>
+          <t>3185728</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121804</t>
+          <t>122091</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161168</t>
+          <t>162265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155671</t>
+          <t>155963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194672</t>
+          <t>194178</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>285171</t>
+          <t>287852</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>343066</t>
+          <t>344430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>258295</t>
+          <t>257198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>297659</t>
+          <t>297372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201083</t>
+          <t>201577</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>240084</t>
+          <t>239792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>472152</t>
+          <t>470788</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>530047</t>
+          <t>527366</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>248080</t>
+          <t>245315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>294905</t>
+          <t>295141</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>250945</t>
+          <t>255547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>298620</t>
+          <t>301731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>514523</t>
+          <t>513006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>584234</t>
+          <t>583283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,54%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>295591</t>
+          <t>295355</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342416</t>
+          <t>345181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264924</t>
+          <t>261813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>312599</t>
+          <t>307997</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>569806</t>
+          <t>570757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>639517</t>
+          <t>641034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,55%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>295524</t>
+          <t>295334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>346899</t>
+          <t>347309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>300904</t>
+          <t>303618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>352862</t>
+          <t>353462</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>609309</t>
+          <t>616430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>682872</t>
+          <t>688838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,77%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322198</t>
+          <t>321788</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>373573</t>
+          <t>373763</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308524</t>
+          <t>307924</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>360482</t>
+          <t>357768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647611</t>
+          <t>641645</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>721174</t>
+          <t>714053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>319546</t>
+          <t>316646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>372329</t>
+          <t>370428</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>366991</t>
+          <t>365429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>417327</t>
+          <t>417768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>702194</t>
+          <t>702970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>772804</t>
+          <t>771865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,6%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>273719</t>
+          <t>275620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326502</t>
+          <t>329402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231750</t>
+          <t>231309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>282086</t>
+          <t>283648</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>522321</t>
+          <t>523260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>592931</t>
+          <t>592155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>223775</t>
+          <t>225274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>269732</t>
+          <t>270554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>283991</t>
+          <t>285069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>331472</t>
+          <t>330476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>524551</t>
+          <t>522993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>590319</t>
+          <t>587031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>208186</t>
+          <t>207364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>254143</t>
+          <t>252644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165377</t>
+          <t>166373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>212858</t>
+          <t>211780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384448</t>
+          <t>387736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>450216</t>
+          <t>451774</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>150808</t>
+          <t>150916</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>188806</t>
+          <t>187435</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>202519</t>
+          <t>202157</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>240738</t>
+          <t>242883</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>364485</t>
+          <t>363905</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>420346</t>
+          <t>416815</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145524</t>
+          <t>146895</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183522</t>
+          <t>183414</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137024</t>
+          <t>134879</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>175243</t>
+          <t>175605</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>291746</t>
+          <t>295277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>347607</t>
+          <t>348187</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124036</t>
+          <t>123980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153326</t>
+          <t>152435</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>217675</t>
+          <t>220157</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262742</t>
+          <t>263281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>353023</t>
+          <t>355394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>405896</t>
+          <t>409372</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,29%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103672</t>
+          <t>104563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>132962</t>
+          <t>133018</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137427</t>
+          <t>136888</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>182494</t>
+          <t>180012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>251271</t>
+          <t>247795</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>304144</t>
+          <t>301773</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1575082</t>
+          <t>1578751</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1691855</t>
+          <t>1701411</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1882208</t>
+          <t>1884984</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2005086</t>
+          <t>2012236</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3498469</t>
+          <t>3483912</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3664912</t>
+          <t>3659063</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1702495</t>
+          <t>1692939</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1819268</t>
+          <t>1815599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1539456</t>
+          <t>1532306</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1662334</t>
+          <t>1659558</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3273980</t>
+          <t>3279829</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3440423</t>
+          <t>3454980</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76018</t>
+          <t>75360</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134921</t>
+          <t>136260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98972</t>
+          <t>99749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146168</t>
+          <t>145793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188204</t>
+          <t>188438</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>269073</t>
+          <t>266099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265066</t>
+          <t>263727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>323969</t>
+          <t>324627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165449</t>
+          <t>165824</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212645</t>
+          <t>211868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>442531</t>
+          <t>445505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>523400</t>
+          <t>523166</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119350</t>
+          <t>118149</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169021</t>
+          <t>169830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194175</t>
+          <t>194192</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346776</t>
+          <t>346211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>332972</t>
+          <t>328868</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>515184</t>
+          <t>526946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>254526</t>
+          <t>253717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>304197</t>
+          <t>305398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164188</t>
+          <t>164753</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316789</t>
+          <t>316772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>419327</t>
+          <t>407565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601539</t>
+          <t>605643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,81%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169975</t>
+          <t>168353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215779</t>
+          <t>215353</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219712</t>
+          <t>220768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256218</t>
+          <t>258457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>402009</t>
+          <t>403244</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>463331</t>
+          <t>462862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,97%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>319590</t>
+          <t>320016</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>365394</t>
+          <t>367016</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>285540</t>
+          <t>283301</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>322046</t>
+          <t>320990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613797</t>
+          <t>614266</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675119</t>
+          <t>673884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,56%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120392</t>
+          <t>113836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>404851</t>
+          <t>400140</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>295832</t>
+          <t>293405</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381070</t>
+          <t>379934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>361775</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>765610</t>
+          <t>765739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>480840</t>
+          <t>485551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>765299</t>
+          <t>771855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328242</t>
+          <t>329378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>413480</t>
+          <t>415907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>829393</t>
+          <t>829264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1233228</t>
+          <t>1231287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>248523</t>
+          <t>252777</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>293722</t>
+          <t>297560</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>293567</t>
+          <t>294172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>327291</t>
+          <t>328192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>555672</t>
+          <t>556364</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>614742</t>
+          <t>615933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>261215</t>
+          <t>257377</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>306414</t>
+          <t>302160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>218310</t>
+          <t>217409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>252034</t>
+          <t>251429</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>485796</t>
+          <t>484605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>544866</t>
+          <t>544174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>161215</t>
+          <t>164252</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>192558</t>
+          <t>192836</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>325047</t>
+          <t>325757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>529222</t>
+          <t>533218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>497787</t>
+          <t>497780</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>767784</t>
+          <t>771703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,52%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>171203</t>
+          <t>170925</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202546</t>
+          <t>199509</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77421</t>
+          <t>73425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>281596</t>
+          <t>280886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>202621</t>
+          <t>198702</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>472618</t>
+          <t>472625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142916</t>
+          <t>141896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168795</t>
+          <t>167007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252334</t>
+          <t>252066</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>279537</t>
+          <t>280404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>401602</t>
+          <t>402190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>440165</t>
+          <t>441283</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>111623</t>
+          <t>113411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137502</t>
+          <t>138522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>138171</t>
+          <t>137304</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165374</t>
+          <t>165642</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>257961</t>
+          <t>256843</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>296524</t>
+          <t>295936</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>976902</t>
+          <t>1052445</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1447636</t>
+          <t>1456307</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1823309</t>
+          <t>1827309</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2243155</t>
+          <t>2268094</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2972898</t>
+          <t>2972143</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3602461</t>
+          <t>3633796</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1996075</t>
+          <t>1987404</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2466809</t>
+          <t>2391266</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1400448</t>
+          <t>1375509</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1820294</t>
+          <t>1816294</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3484853</t>
+          <t>3453518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4114416</t>
+          <t>4115171</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>138800</t>
+          <t>137843</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>179080</t>
+          <t>180292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>179663</t>
+          <t>179782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220539</t>
+          <t>222766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>330703</t>
+          <t>331165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>390176</t>
+          <t>389391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>314984</t>
+          <t>313772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355264</t>
+          <t>356221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246950</t>
+          <t>244723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287826</t>
+          <t>287707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>571377</t>
+          <t>572162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>630850</t>
+          <t>630388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230931</t>
+          <t>227107</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>280456</t>
+          <t>280295</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>278497</t>
+          <t>278570</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>329391</t>
+          <t>328298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>524290</t>
+          <t>522622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>595734</t>
+          <t>595768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455033</t>
+          <t>455194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504558</t>
+          <t>508382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296103</t>
+          <t>297196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>346997</t>
+          <t>346924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>765248</t>
+          <t>765214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>836692</t>
+          <t>838360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>252290</t>
+          <t>250973</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>306203</t>
+          <t>303022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>373700</t>
+          <t>375300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>428926</t>
+          <t>428003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>647623</t>
+          <t>642892</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>715925</t>
+          <t>715756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>332465</t>
+          <t>335646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>387695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260818</t>
+          <t>261741</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316044</t>
+          <t>314444</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>612487</t>
+          <t>612656</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680789</t>
+          <t>685520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211625</t>
+          <t>211777</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>257941</t>
+          <t>257436</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>300237</t>
+          <t>301075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>344864</t>
+          <t>345651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>522273</t>
+          <t>524703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>587914</t>
+          <t>586583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>261206</t>
+          <t>261711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>307522</t>
+          <t>307370</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170778</t>
+          <t>169991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215405</t>
+          <t>214567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>446875</t>
+          <t>448206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>512516</t>
+          <t>510086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>197201</t>
+          <t>196328</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>238022</t>
+          <t>233367</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>218838</t>
+          <t>216436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>258174</t>
+          <t>257961</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>427016</t>
+          <t>423514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>484017</t>
+          <t>480745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148688</t>
+          <t>153343</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>189509</t>
+          <t>190382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145812</t>
+          <t>146025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185148</t>
+          <t>187550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306679</t>
+          <t>309951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363680</t>
+          <t>367182</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,44%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141528</t>
+          <t>141986</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175895</t>
+          <t>174144</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>177176</t>
+          <t>177121</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>211622</t>
+          <t>213645</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>331835</t>
+          <t>330590</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>380219</t>
+          <t>377421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116688</t>
+          <t>118439</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151055</t>
+          <t>150597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131312</t>
+          <t>129289</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>165758</t>
+          <t>165813</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>255298</t>
+          <t>258096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>303682</t>
+          <t>304927</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99940</t>
+          <t>100657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>129291</t>
+          <t>128202</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150156</t>
+          <t>149060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186824</t>
+          <t>188759</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261032</t>
+          <t>258652</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>305440</t>
+          <t>306175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,3%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80592</t>
+          <t>81681</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109943</t>
+          <t>109226</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>147084</t>
+          <t>145149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>183752</t>
+          <t>184848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>238351</t>
+          <t>237616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>285139</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1359326</t>
+          <t>1359732</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1474346</t>
+          <t>1472819</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1770768</t>
+          <t>1773654</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1893868</t>
+          <t>1890895</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3159395</t>
+          <t>3161364</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3321312</t>
+          <t>3326987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1802197</t>
+          <t>1803724</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1917217</t>
+          <t>1916811</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1485329</t>
+          <t>1488302</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1608429</t>
+          <t>1605543</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3334429</t>
+          <t>3328754</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3496346</t>
+          <t>3494377</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139018</t>
+          <t>140596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181152</t>
+          <t>180487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192100</t>
+          <t>189371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>233165</t>
+          <t>233167</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>342855</t>
+          <t>341990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>400277</t>
+          <t>400094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,24%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272994</t>
+          <t>273659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>315128</t>
+          <t>313550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197065</t>
+          <t>197063</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238130</t>
+          <t>240859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>484099</t>
+          <t>484282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>541521</t>
+          <t>542386</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>279757</t>
+          <t>277615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>334066</t>
+          <t>330008</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>312935</t>
+          <t>312304</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>364796</t>
+          <t>362451</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>606594</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>680481</t>
+          <t>681480</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,53%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353021</t>
+          <t>357079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407330</t>
+          <t>409472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>245459</t>
+          <t>247804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>297320</t>
+          <t>297951</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>616861</t>
+          <t>615862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>690748</t>
+          <t>688487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>319946</t>
+          <t>318705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>374084</t>
+          <t>374392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>424174</t>
+          <t>425379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>481088</t>
+          <t>477949</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>760064</t>
+          <t>764577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>836641</t>
+          <t>837246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,12%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307779</t>
+          <t>307471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>361917</t>
+          <t>363158</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>229762</t>
+          <t>232901</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286676</t>
+          <t>285471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>556071</t>
+          <t>555466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632648</t>
+          <t>628135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>303973</t>
+          <t>304442</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>356194</t>
+          <t>357375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>370624</t>
+          <t>368213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>420476</t>
+          <t>418009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>691214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>762624</t>
+          <t>763369</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,02%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>258423</t>
+          <t>257242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310644</t>
+          <t>310175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195723</t>
+          <t>198190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245575</t>
+          <t>247986</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>468192</t>
+          <t>467447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>536961</t>
+          <t>539602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>214460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>257552</t>
+          <t>256978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287071</t>
+          <t>286366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>326885</t>
+          <t>328452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>515417</t>
+          <t>514823</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>575818</t>
+          <t>573943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171877</t>
+          <t>172451</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>215826</t>
+          <t>214969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120915</t>
+          <t>119348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160729</t>
+          <t>161434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>301411</t>
+          <t>303286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361812</t>
+          <t>362406</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138375</t>
+          <t>138096</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175511</t>
+          <t>173865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>211167</t>
+          <t>210511</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>247537</t>
+          <t>247228</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>357055</t>
+          <t>360064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>409963</t>
+          <t>413925</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134275</t>
+          <t>135921</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171411</t>
+          <t>171690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106459</t>
+          <t>106768</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142829</t>
+          <t>143485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253819</t>
+          <t>249857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>306727</t>
+          <t>303718</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>126117</t>
+          <t>126568</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159348</t>
+          <t>159290</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>245740</t>
+          <t>246499</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284163</t>
+          <t>284638</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>380763</t>
+          <t>384432</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>434373</t>
+          <t>432442</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90503</t>
+          <t>90561</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>123734</t>
+          <t>123283</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104816</t>
+          <t>104341</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143239</t>
+          <t>142480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>204457</t>
+          <t>206388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>258067</t>
+          <t>254398</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1621155</t>
+          <t>1617919</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1735304</t>
+          <t>1741217</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2141157</t>
+          <t>2141732</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2255406</t>
+          <t>2263726</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3799360</t>
+          <t>3797016</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3968661</t>
+          <t>3961862</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,72%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1691475</t>
+          <t>1685562</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1805624</t>
+          <t>1808860</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1302903</t>
+          <t>1294583</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1417152</t>
+          <t>1416577</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3016427</t>
+          <t>3023226</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3185728</t>
+          <t>3188072</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122091</t>
+          <t>121056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>162265</t>
+          <t>160777</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155963</t>
+          <t>154804</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194178</t>
+          <t>192580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287852</t>
+          <t>289223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>344430</t>
+          <t>343908</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,19%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257198</t>
+          <t>258686</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>297372</t>
+          <t>298407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201577</t>
+          <t>203175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239792</t>
+          <t>240951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>470788</t>
+          <t>471310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>527366</t>
+          <t>525995</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>245315</t>
+          <t>246900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>295141</t>
+          <t>298066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>255547</t>
+          <t>254935</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>301731</t>
+          <t>300356</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>513177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>583283</t>
+          <t>581563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>295355</t>
+          <t>292430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>345181</t>
+          <t>343596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>261813</t>
+          <t>263188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>307997</t>
+          <t>308609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>570757</t>
+          <t>572477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>641034</t>
+          <t>640863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>295334</t>
+          <t>294706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>347309</t>
+          <t>347701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>303618</t>
+          <t>302355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>353462</t>
+          <t>353405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>616430</t>
+          <t>613987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>688838</t>
+          <t>687198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>321788</t>
+          <t>321396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>373763</t>
+          <t>374391</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307924</t>
+          <t>307981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>357768</t>
+          <t>359031</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641645</t>
+          <t>643285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>714053</t>
+          <t>716496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316646</t>
+          <t>316759</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>370428</t>
+          <t>369760</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>365429</t>
+          <t>369431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>417768</t>
+          <t>417116</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>702970</t>
+          <t>700622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>771865</t>
+          <t>777367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275620</t>
+          <t>276288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>329402</t>
+          <t>329289</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231309</t>
+          <t>231961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283648</t>
+          <t>279646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>523260</t>
+          <t>517758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>592155</t>
+          <t>594503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>225274</t>
+          <t>224475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>270554</t>
+          <t>271069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>285069</t>
+          <t>283720</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>330476</t>
+          <t>328304</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>522993</t>
+          <t>521531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>587031</t>
+          <t>588798</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>207364</t>
+          <t>206849</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>252644</t>
+          <t>253443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166373</t>
+          <t>168545</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211780</t>
+          <t>213129</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>387736</t>
+          <t>385969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>451774</t>
+          <t>453236</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>150916</t>
+          <t>150768</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>187435</t>
+          <t>188710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>202157</t>
+          <t>200771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>242883</t>
+          <t>241285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>363905</t>
+          <t>363268</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>416815</t>
+          <t>415425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146895</t>
+          <t>145620</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183414</t>
+          <t>183562</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>134879</t>
+          <t>136477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>175605</t>
+          <t>176991</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>295277</t>
+          <t>296667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>348187</t>
+          <t>348824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123980</t>
+          <t>125402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>152435</t>
+          <t>154896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>220157</t>
+          <t>216093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>263281</t>
+          <t>264018</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>355394</t>
+          <t>352485</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>409372</t>
+          <t>408592</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>104563</t>
+          <t>102102</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>133018</t>
+          <t>131596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136888</t>
+          <t>136151</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180012</t>
+          <t>184076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>247795</t>
+          <t>248575</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>301773</t>
+          <t>304682</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1578751</t>
+          <t>1569963</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1701411</t>
+          <t>1684833</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1884984</t>
+          <t>1877885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2012236</t>
+          <t>2002874</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3483912</t>
+          <t>3488953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3659063</t>
+          <t>3660935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1692939</t>
+          <t>1709517</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1815599</t>
+          <t>1824387</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1532306</t>
+          <t>1541668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1659558</t>
+          <t>1666657</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3279829</t>
+          <t>3277957</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3454980</t>
+          <t>3449939</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>103184</t>
+          <t>119506</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75360</t>
+          <t>91665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136260</t>
+          <t>150230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>122000</t>
+          <t>134510</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99749</t>
+          <t>108814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145793</t>
+          <t>159872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>225184</t>
+          <t>254016</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188438</t>
+          <t>213888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>266099</t>
+          <t>291944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>296803</t>
+          <t>288287</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263727</t>
+          <t>257563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>324627</t>
+          <t>316128</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>189617</t>
+          <t>226505</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165824</t>
+          <t>201143</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>211868</t>
+          <t>252201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>486420</t>
+          <t>514793</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>445505</t>
+          <t>476865</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>523166</t>
+          <t>554921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>711604</t>
+          <t>768809</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>143406</t>
+          <t>163176</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118149</t>
+          <t>137881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169830</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>244013</t>
+          <t>202386</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194192</t>
+          <t>178989</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346211</t>
+          <t>226262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>387419</t>
+          <t>365563</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>328868</t>
+          <t>332037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>526946</t>
+          <t>401289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>280141</t>
+          <t>313714</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253717</t>
+          <t>288762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>305398</t>
+          <t>339009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>266951</t>
+          <t>298118</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164753</t>
+          <t>274242</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316772</t>
+          <t>321515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>547092</t>
+          <t>611831</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>407565</t>
+          <t>576105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>605643</t>
+          <t>645357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>510964</t>
+          <t>500504</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934511</t>
+          <t>977394</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>193411</t>
+          <t>224126</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168353</t>
+          <t>201053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215353</t>
+          <t>249261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>238605</t>
+          <t>282361</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>220768</t>
+          <t>262323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>258457</t>
+          <t>302472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>432016</t>
+          <t>506487</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>403244</t>
+          <t>472440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>462862</t>
+          <t>538830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>341958</t>
+          <t>395723</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>320016</t>
+          <t>370588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>367016</t>
+          <t>418796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>303153</t>
+          <t>338997</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283301</t>
+          <t>318886</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>320990</t>
+          <t>359035</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>645112</t>
+          <t>734720</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>614266</t>
+          <t>702377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673884</t>
+          <t>768767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>61,94%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535369</t>
+          <t>619849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>621358</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>621358</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541758</t>
+          <t>621358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1077128</t>
+          <t>1241207</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1077128</t>
+          <t>1241207</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1077128</t>
+          <t>1241207</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>283870</t>
+          <t>303351</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113836</t>
+          <t>275502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>400140</t>
+          <t>332627</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>353174</t>
+          <t>381377</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>293405</t>
+          <t>358734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>379934</t>
+          <t>403071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>637044</t>
+          <t>684728</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>363716</t>
+          <t>647141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>765739</t>
+          <t>718157</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>601821</t>
+          <t>395228</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>485551</t>
+          <t>365952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>771855</t>
+          <t>423077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>356138</t>
+          <t>351819</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>329378</t>
+          <t>330125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>415907</t>
+          <t>374462</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>51,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>957959</t>
+          <t>747047</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>829264</t>
+          <t>713618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1231287</t>
+          <t>784634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>885691</t>
+          <t>698579</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>885691</t>
+          <t>698579</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>885691</t>
+          <t>698579</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>709312</t>
+          <t>733196</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>709312</t>
+          <t>733196</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>709312</t>
+          <t>733196</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1595003</t>
+          <t>1431775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1595003</t>
+          <t>1431775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1595003</t>
+          <t>1431775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>273344</t>
+          <t>294214</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>252777</t>
+          <t>271133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>297560</t>
+          <t>316264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>310590</t>
+          <t>350506</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>294172</t>
+          <t>332434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>328192</t>
+          <t>369223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>583934</t>
+          <t>644720</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>556364</t>
+          <t>613606</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>615933</t>
+          <t>673988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>281593</t>
+          <t>308076</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>257377</t>
+          <t>286026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>302160</t>
+          <t>331157</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>235011</t>
+          <t>255979</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>217409</t>
+          <t>237262</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>251429</t>
+          <t>274051</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>516604</t>
+          <t>564055</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>484605</t>
+          <t>534787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>544174</t>
+          <t>595169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>554937</t>
+          <t>602290</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>554937</t>
+          <t>602290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>554937</t>
+          <t>602290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545601</t>
+          <t>606485</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545601</t>
+          <t>606485</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545601</t>
+          <t>606485</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1100538</t>
+          <t>1208775</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1100538</t>
+          <t>1208775</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1100538</t>
+          <t>1208775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>178299</t>
+          <t>195363</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>164252</t>
+          <t>179424</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>192836</t>
+          <t>212530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>425624</t>
+          <t>244552</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>325757</t>
+          <t>230228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>533218</t>
+          <t>259688</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>603923</t>
+          <t>439915</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>497780</t>
+          <t>417774</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>771703</t>
+          <t>462403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>185462</t>
+          <t>206729</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170925</t>
+          <t>189562</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>199509</t>
+          <t>222668</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>181019</t>
+          <t>192698</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73425</t>
+          <t>177562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280886</t>
+          <t>207022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>366482</t>
+          <t>399427</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198702</t>
+          <t>376939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>472625</t>
+          <t>421568</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>363761</t>
+          <t>402092</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>363761</t>
+          <t>402092</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>363761</t>
+          <t>402092</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>606643</t>
+          <t>437250</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>606643</t>
+          <t>437250</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>606643</t>
+          <t>437250</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>970405</t>
+          <t>839342</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>970405</t>
+          <t>839342</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>970405</t>
+          <t>839342</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>155029</t>
+          <t>171245</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141896</t>
+          <t>156194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167007</t>
+          <t>185856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>266424</t>
+          <t>290495</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252066</t>
+          <t>273786</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>280404</t>
+          <t>305306</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>421453</t>
+          <t>461740</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>402190</t>
+          <t>441995</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>441283</t>
+          <t>482305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>125389</t>
+          <t>136364</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>113411</t>
+          <t>121753</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138522</t>
+          <t>151415</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>151284</t>
+          <t>165324</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>137304</t>
+          <t>150513</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165642</t>
+          <t>182033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>276673</t>
+          <t>301688</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>256843</t>
+          <t>281123</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>295936</t>
+          <t>321433</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>280418</t>
+          <t>307609</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>280418</t>
+          <t>307609</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>280418</t>
+          <t>307609</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>417708</t>
+          <t>455819</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>417708</t>
+          <t>455819</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>417708</t>
+          <t>455819</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>698126</t>
+          <t>763428</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>698126</t>
+          <t>763428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>698126</t>
+          <t>763428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1330544</t>
+          <t>1470982</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1052445</t>
+          <t>1407074</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1456307</t>
+          <t>1533452</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1960429</t>
+          <t>1886188</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1827309</t>
+          <t>1836258</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2268094</t>
+          <t>1940212</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,17 +12136,17 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3290973</t>
+          <t>3357170</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2972143</t>
+          <t>3275867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3633796</t>
+          <t>3442213</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2113167</t>
+          <t>2044121</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1987404</t>
+          <t>1981651</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2391266</t>
+          <t>2108029</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1683174</t>
+          <t>1829439</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1375509</t>
+          <t>1775415</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1816294</t>
+          <t>1879369</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,17 +12249,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3796341</t>
+          <t>3873560</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3453518</t>
+          <t>3788517</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4115171</t>
+          <t>3954863</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
